--- a/감사조서_개선템플릿_2025_VER2.xlsx
+++ b/감사조서_개선템플릿_2025_VER2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{5EFC5DFD-0E53-4792-95BF-94B732752290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기본사항" sheetId="1" r:id="rId1"/>
@@ -1413,22 +1413,10 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1438,7 +1426,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1453,27 +1453,14 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1482,34 +1469,47 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1826,38 +1826,38 @@
   <sheetData>
     <row r="1" spans="1:5" ht="8" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5" ht="10" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="37"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
+      <c r="A4" s="45"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5" ht="10" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
@@ -1868,10 +1868,10 @@
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3"/>
@@ -1881,10 +1881,10 @@
       <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="34"/>
+      <c r="E8" s="41"/>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3"/>
@@ -1894,10 +1894,10 @@
       <c r="C9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="34"/>
+      <c r="E9" s="41"/>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3"/>
@@ -1907,54 +1907,54 @@
       <c r="C10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="34"/>
+      <c r="E10" s="41"/>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:5" ht="10" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
     </row>
     <row r="14" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="34"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="41"/>
     </row>
     <row r="15" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="34"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="41"/>
     </row>
     <row r="16" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="34"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="41"/>
     </row>
     <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -1966,6 +1966,11 @@
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D10:E10"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A13:E13"/>
@@ -1973,11 +1978,6 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1998,142 +1998,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>243</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="38"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="38"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="74" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="38"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -2299,18 +2299,18 @@
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="14" t="s">
@@ -2325,12 +2325,12 @@
       <c r="D22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="73"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
@@ -2339,12 +2339,12 @@
       <c r="B23" s="22"/>
       <c r="C23" s="23"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
@@ -2353,12 +2353,12 @@
       <c r="B24" s="22"/>
       <c r="C24" s="23"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21" t="s">
@@ -2367,12 +2367,12 @@
       <c r="B25" s="22"/>
       <c r="C25" s="23"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21" t="s">
@@ -2381,12 +2381,12 @@
       <c r="B26" s="22"/>
       <c r="C26" s="23"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="21" t="s">
@@ -2395,12 +2395,12 @@
       <c r="B27" s="22"/>
       <c r="C27" s="23"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="21" t="s">
@@ -2409,28 +2409,28 @@
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
@@ -2439,12 +2439,12 @@
       <c r="B32" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="F32" s="38"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="13" t="s">
         <v>224</v>
       </c>
@@ -2454,253 +2454,253 @@
       <c r="I32" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="38"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="29">
         <v>1</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="67" t="s">
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="F33" s="38"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="38"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="29">
         <v>2</v>
       </c>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="68" t="s">
         <v>258</v>
       </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="67" t="s">
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="66" t="s">
         <v>231</v>
       </c>
-      <c r="F34" s="38"/>
+      <c r="F34" s="34"/>
       <c r="G34" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H34" s="32"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="38"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="34"/>
     </row>
     <row r="35" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="29">
         <v>3</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="67" t="s">
         <v>259</v>
       </c>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="67" t="s">
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="66" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="38"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H35" s="11"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="38"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="29">
         <v>4</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="67" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="F36" s="38"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H36" s="32"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="38"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="34"/>
     </row>
     <row r="37" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="29">
         <v>5</v>
       </c>
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="67" t="s">
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="F37" s="38"/>
+      <c r="F37" s="34"/>
       <c r="G37" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H37" s="11"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="38"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="34"/>
     </row>
     <row r="38" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="29">
         <v>6</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>264</v>
       </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="67" t="s">
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="66" t="s">
         <v>262</v>
       </c>
-      <c r="F38" s="38"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H38" s="32"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="38"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="34"/>
     </row>
     <row r="39" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="29">
         <v>7</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="67" t="s">
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="66" t="s">
         <v>266</v>
       </c>
-      <c r="F39" s="38"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H39" s="11"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="38"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="34"/>
     </row>
     <row r="40" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="29">
         <v>8</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="67" t="s">
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="F40" s="38"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H40" s="32"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="38"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="34"/>
     </row>
     <row r="41" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="29">
         <v>9</v>
       </c>
-      <c r="B41" s="70" t="s">
+      <c r="B41" s="67" t="s">
         <v>269</v>
       </c>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="67" t="s">
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="66" t="s">
         <v>241</v>
       </c>
-      <c r="F41" s="38"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H41" s="11"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="38"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="34"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="43" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="62" t="s">
+      <c r="A43" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="68"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="A44" s="69"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
     </row>
     <row r="45" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="68"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
     </row>
     <row r="46" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="68"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
+      <c r="A46" s="69"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
     </row>
     <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="65" t="s">
+      <c r="A48" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
     </row>
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2735,21 +2735,23 @@
     <row r="79" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="E25:J25"/>
@@ -2766,31 +2768,30 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E41:F41"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="I35:J35"/>
@@ -2799,7 +2800,6 @@
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2824,35 +2824,35 @@
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
     </row>
     <row r="6" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
@@ -2959,10 +2959,10 @@
       <c r="A16" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
     </row>
     <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="18" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -3014,104 +3014,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -3121,35 +3121,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -3267,18 +3267,18 @@
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="18" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="64"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="60"/>
     </row>
     <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="14" t="s">
@@ -3293,12 +3293,12 @@
       <c r="D19" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="52"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="34"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="41"/>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="21" t="s">
@@ -3307,12 +3307,12 @@
       <c r="B20" s="22"/>
       <c r="C20" s="23"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="34"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="41"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="21" t="s">
@@ -3321,12 +3321,12 @@
       <c r="B21" s="22"/>
       <c r="C21" s="23"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="34"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="21" t="s">
@@ -3335,139 +3335,139 @@
       <c r="B22" s="22"/>
       <c r="C22" s="23"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="34"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="25" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="45"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="39"/>
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="54" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="34"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="41"/>
     </row>
     <row r="27" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="51" t="s">
+      <c r="A27" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="54" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="34"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="54" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="34"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="54" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="34"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="54" t="s">
+      <c r="B30" s="41"/>
+      <c r="C30" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="33" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="65" t="s">
+      <c r="A33" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="38"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -3487,6 +3487,27 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="E19:J19"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A26:B26"/>
@@ -3503,27 +3524,6 @@
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="G5:J5"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="C31:J31"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3544,104 +3544,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -3651,35 +3651,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -3829,18 +3829,18 @@
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="60"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="14" t="s">
@@ -3855,12 +3855,12 @@
       <c r="D21" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="34"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="21" t="s">
@@ -3869,12 +3869,12 @@
       <c r="B22" s="22"/>
       <c r="C22" s="23"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="34"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
@@ -3883,12 +3883,12 @@
       <c r="B23" s="22"/>
       <c r="C23" s="23"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="34"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="41"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
@@ -3897,12 +3897,12 @@
       <c r="B24" s="22"/>
       <c r="C24" s="23"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="34"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21" t="s">
@@ -3911,12 +3911,12 @@
       <c r="B25" s="22"/>
       <c r="C25" s="23"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="34"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="41"/>
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21" t="s">
@@ -3925,139 +3925,139 @@
       <c r="B26" s="22"/>
       <c r="C26" s="23"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="34"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="41"/>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="29" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="45"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="39"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="54" t="s">
+      <c r="B30" s="41"/>
+      <c r="C30" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="54" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="34"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="41"/>
+      <c r="C33" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="34"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="41"/>
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="54" t="s">
+      <c r="B34" s="41"/>
+      <c r="C34" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="34"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="41"/>
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="51" t="s">
+      <c r="A35" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="54" t="s">
+      <c r="B35" s="41"/>
+      <c r="C35" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="34"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="41"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="37" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="65" t="s">
+      <c r="A37" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4073,14 +4073,13 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="C32:J32"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E22:J22"/>
@@ -4092,24 +4091,25 @@
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="G5:J5"/>
-    <mergeCell ref="C35:J35"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="E26:J26"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C35:J35"/>
     <mergeCell ref="C31:J31"/>
     <mergeCell ref="E25:J25"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C34:J34"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C33:J33"/>
   </mergeCells>
@@ -4132,104 +4132,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -4239,35 +4239,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -4465,18 +4465,18 @@
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="23" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="64"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
@@ -4491,12 +4491,12 @@
       <c r="D24" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="34"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21" t="s">
@@ -4505,12 +4505,12 @@
       <c r="B25" s="22"/>
       <c r="C25" s="23"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="34"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="41"/>
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21" t="s">
@@ -4519,12 +4519,12 @@
       <c r="B26" s="22"/>
       <c r="C26" s="23"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="34"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="41"/>
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="21" t="s">
@@ -4533,12 +4533,12 @@
       <c r="B27" s="22"/>
       <c r="C27" s="23"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="34"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="21" t="s">
@@ -4547,12 +4547,12 @@
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="34"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="21" t="s">
@@ -4561,12 +4561,12 @@
       <c r="B29" s="22"/>
       <c r="C29" s="23"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="34"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="21" t="s">
@@ -4575,12 +4575,12 @@
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="21" t="s">
@@ -4589,12 +4589,12 @@
       <c r="B31" s="22"/>
       <c r="C31" s="23"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="21" t="s">
@@ -4603,139 +4603,139 @@
       <c r="B32" s="22"/>
       <c r="C32" s="23"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="34"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="45"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="39"/>
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="54" t="s">
+      <c r="B36" s="41"/>
+      <c r="C36" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="34"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="41"/>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="54" t="s">
+      <c r="B37" s="41"/>
+      <c r="C37" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="34"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="41"/>
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="54" t="s">
+      <c r="B38" s="41"/>
+      <c r="C38" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="34"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="41"/>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="54" t="s">
+      <c r="B39" s="41"/>
+      <c r="C39" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="34"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="41"/>
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="54" t="s">
+      <c r="B40" s="41"/>
+      <c r="C40" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="34"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="41"/>
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="54" t="s">
+      <c r="B41" s="41"/>
+      <c r="C41" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="34"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="41"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="43" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="65" t="s">
+      <c r="A43" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4745,20 +4745,16 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E29:J29"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E28:J28"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="E27:J27"/>
@@ -4775,18 +4771,22 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="E31:J31"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4807,104 +4807,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -4914,35 +4914,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -5076,18 +5076,18 @@
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="64"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="60"/>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="14" t="s">
@@ -5102,12 +5102,12 @@
       <c r="D20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="34"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="41"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="21" t="s">
@@ -5116,12 +5116,12 @@
       <c r="B21" s="22"/>
       <c r="C21" s="23"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="34"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="21" t="s">
@@ -5130,12 +5130,12 @@
       <c r="B22" s="22"/>
       <c r="C22" s="23"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="34"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
@@ -5144,12 +5144,12 @@
       <c r="B23" s="22"/>
       <c r="C23" s="23"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="34"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="41"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
@@ -5158,139 +5158,139 @@
       <c r="B24" s="22"/>
       <c r="C24" s="23"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="34"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="27" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="45"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="39"/>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="54" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="34"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="54" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="34"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="54" t="s">
+      <c r="B30" s="41"/>
+      <c r="C30" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="54" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="34"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="41"/>
+      <c r="C33" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="34"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="41"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5308,6 +5308,28 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E22:J22"/>
@@ -5324,28 +5346,6 @@
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="C32:J32"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="C31:J31"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="C33:J33"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5366,104 +5366,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -5473,35 +5473,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -5635,18 +5635,18 @@
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="64"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="60"/>
     </row>
     <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="14" t="s">
@@ -5661,12 +5661,12 @@
       <c r="D20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="52"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="34"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="41"/>
     </row>
     <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="21" t="s">
@@ -5675,12 +5675,12 @@
       <c r="B21" s="22"/>
       <c r="C21" s="23"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="34"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="21" t="s">
@@ -5689,12 +5689,12 @@
       <c r="B22" s="22"/>
       <c r="C22" s="23"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="34"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
@@ -5703,12 +5703,12 @@
       <c r="B23" s="22"/>
       <c r="C23" s="23"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="34"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="41"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
@@ -5717,139 +5717,139 @@
       <c r="B24" s="22"/>
       <c r="C24" s="23"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="34"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="27" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="45"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="39"/>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="54" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="34"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="54" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="34"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="54" t="s">
+      <c r="B30" s="41"/>
+      <c r="C30" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="51" t="s">
+      <c r="A31" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="62" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="52" t="s">
         <v>172</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="54" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="62" t="s">
         <v>173</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="34"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="41"/>
+      <c r="C33" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="34"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="41"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5867,6 +5867,28 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E22:J22"/>
@@ -5883,28 +5905,6 @@
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="C32:J32"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="C31:J31"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="C33:J33"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5925,104 +5925,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="53"/>
-      <c r="D5" s="34"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="53"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="34"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="53"/>
-      <c r="D6" s="34"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="34"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="53"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="26"/>
-      <c r="C7" s="61" t="str">
+      <c r="C7" s="56" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="13"/>
       <c r="F7" s="26"/>
       <c r="G7" s="13"/>
@@ -6032,35 +6032,35 @@
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="34"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -6258,18 +6258,18 @@
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="23" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="64"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="14" t="s">
@@ -6284,12 +6284,12 @@
       <c r="D24" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="34"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="41"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21" t="s">
@@ -6298,12 +6298,12 @@
       <c r="B25" s="22"/>
       <c r="C25" s="23"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="34"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="41"/>
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21" t="s">
@@ -6312,12 +6312,12 @@
       <c r="B26" s="22"/>
       <c r="C26" s="23"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="34"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="41"/>
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="21" t="s">
@@ -6326,12 +6326,12 @@
       <c r="B27" s="22"/>
       <c r="C27" s="23"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="34"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="21" t="s">
@@ -6340,12 +6340,12 @@
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="34"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="21" t="s">
@@ -6354,12 +6354,12 @@
       <c r="B29" s="22"/>
       <c r="C29" s="23"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="34"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="41"/>
     </row>
     <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="21" t="s">
@@ -6368,12 +6368,12 @@
       <c r="B30" s="22"/>
       <c r="C30" s="23"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="34"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="41"/>
     </row>
     <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="21" t="s">
@@ -6382,12 +6382,12 @@
       <c r="B31" s="22"/>
       <c r="C31" s="23"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="34"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="41"/>
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="21" t="s">
@@ -6396,139 +6396,139 @@
       <c r="B32" s="22"/>
       <c r="C32" s="23"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="34"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="41"/>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="45"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="39"/>
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="54" t="s">
+      <c r="B36" s="41"/>
+      <c r="C36" s="62" t="s">
         <v>195</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="34"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="41"/>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="54" t="s">
+      <c r="B37" s="41"/>
+      <c r="C37" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="34"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="41"/>
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="54" t="s">
+      <c r="B38" s="41"/>
+      <c r="C38" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="34"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="41"/>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="54" t="s">
+      <c r="B39" s="41"/>
+      <c r="C39" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="34"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="41"/>
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="54" t="s">
+      <c r="B40" s="41"/>
+      <c r="C40" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="34"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="41"/>
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="54" t="s">
+      <c r="B41" s="41"/>
+      <c r="C41" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="34"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="41"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="43" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="65" t="s">
+      <c r="A43" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -6538,20 +6538,16 @@
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E32:J32"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E29:J29"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E28:J28"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="E27:J27"/>
@@ -6568,18 +6564,22 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="E31:J31"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E32:J32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6600,142 +6600,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="str">
+      <c r="A2" s="61" t="str">
         <f>기본사항!C8</f>
         <v>주식회사 XXX</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="58" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="63" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
     </row>
     <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="38"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="38"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
     </row>
     <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="74" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="28"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="60" t="str">
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="55" t="str">
         <f>기본사항!C10</f>
         <v>2025-12-31</v>
       </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="56" t="s">
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="38"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="14" t="s">
@@ -6901,18 +6901,18 @@
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
     </row>
     <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="14" t="s">
@@ -6927,12 +6927,12 @@
       <c r="D22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="73"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
     </row>
     <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
@@ -6941,12 +6941,12 @@
       <c r="B23" s="22"/>
       <c r="C23" s="23"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
@@ -6955,12 +6955,12 @@
       <c r="B24" s="22"/>
       <c r="C24" s="23"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="21" t="s">
@@ -6969,12 +6969,12 @@
       <c r="B25" s="22"/>
       <c r="C25" s="23"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="21" t="s">
@@ -6983,12 +6983,12 @@
       <c r="B26" s="22"/>
       <c r="C26" s="23"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="21" t="s">
@@ -6997,12 +6997,12 @@
       <c r="B27" s="22"/>
       <c r="C27" s="23"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
     </row>
     <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="21" t="s">
@@ -7011,28 +7011,28 @@
       <c r="B28" s="22"/>
       <c r="C28" s="23"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="72" t="s">
         <v>220</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
@@ -7041,12 +7041,12 @@
       <c r="B32" s="53" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="F32" s="38"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="13" t="s">
         <v>224</v>
       </c>
@@ -7056,233 +7056,233 @@
       <c r="I32" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="38"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="29">
         <v>1</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="67" t="s">
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="F33" s="38"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H33" s="11"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="38"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="29">
         <v>2</v>
       </c>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="68" t="s">
         <v>228</v>
       </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="67" t="s">
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="F34" s="38"/>
+      <c r="F34" s="34"/>
       <c r="G34" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H34" s="32"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="38"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="34"/>
     </row>
     <row r="35" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="29">
         <v>3</v>
       </c>
-      <c r="B35" s="70" t="s">
+      <c r="B35" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="67" t="s">
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="66" t="s">
         <v>231</v>
       </c>
-      <c r="F35" s="38"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H35" s="11"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="38"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="29">
         <v>4</v>
       </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="68" t="s">
         <v>232</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="67" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="F36" s="38"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H36" s="32"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="38"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="34"/>
     </row>
     <row r="37" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="29">
         <v>5</v>
       </c>
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="67" t="s">
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="66" t="s">
         <v>235</v>
       </c>
-      <c r="F37" s="38"/>
+      <c r="F37" s="34"/>
       <c r="G37" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H37" s="11"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="38"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="34"/>
     </row>
     <row r="38" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="29">
         <v>6</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="67" t="s">
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="66" t="s">
         <v>237</v>
       </c>
-      <c r="F38" s="38"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H38" s="32"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="38"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="34"/>
     </row>
     <row r="39" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="29">
         <v>7</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="67" t="s">
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="F39" s="38"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="30" t="s">
         <v>227</v>
       </c>
       <c r="H39" s="11"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="38"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="34"/>
     </row>
     <row r="40" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="29">
         <v>8</v>
       </c>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="67" t="s">
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="66" t="s">
         <v>241</v>
       </c>
-      <c r="F40" s="38"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="31" t="s">
         <v>227</v>
       </c>
       <c r="H40" s="32"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="38"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="34"/>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="42" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
     </row>
     <row r="43" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="68"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="A43" s="69"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="68"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="A44" s="69"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
     </row>
     <row r="45" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="68"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
     </row>
     <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="65" t="s">
+      <c r="A47" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="49" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -7318,12 +7318,45 @@
     <row r="79" ht="18" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E25:J25"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="E6:F6"/>
@@ -7340,46 +7373,13 @@
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E25:J25"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E28:J28"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I40:J40"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
